--- a/esempio-promax-linee.xlsx
+++ b/esempio-promax-linee.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promo_storico" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promozioni" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clienti" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previsioni_marketing" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +467,20 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>Nello strumento: Gerarchia = “Prevedi business line, poi famiglia”. Piano ProMax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Phase_in_out.Tipo = switch (sostituisce) oppure nuovo (non spegne l’analogo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Previsioni_marketing: mesi indicati dal marketing, usati al posto del modello su quei mesi.</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15057,6 +15072,23 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Gelato_Lancio</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dispensa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
         </is>
       </c>
     </row>
@@ -15071,41 +15103,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Nuovo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Vecchio</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fattore</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Mesi_passaggio</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Data_inizio</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cliente_origine</t>
         </is>
@@ -15114,31 +15151,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>switch</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Gelato_Lancio</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Gelato_Vaniglia</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Esselunga</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Esselunga</t>
         </is>
@@ -15147,31 +15189,112 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>switch</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Gelato_Lancio</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Gelato_Vaniglia</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Conad</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>Conad</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Conad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Snack_Mais</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Snack_Mais</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Conad</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Conad</t>
         </is>
@@ -15770,4 +15893,280 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Prodotto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Pezzi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gelato_Lancio</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gelato_Lancio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gelato_Lancio</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gelato_Lancio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gelato_Lancio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gelato_Lancio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Snack_Proteico</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Esselunga</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>